--- a/results/0916-all/藏南农牧区/tech_selected_summary.xlsx
+++ b/results/0916-all/藏南农牧区/tech_selected_summary.xlsx
@@ -121,22 +121,22 @@
     <t>扎囊县</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 115004.82</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
+    <t>115004.82</t>
+  </si>
+  <si>
+    <t>0.00</t>
   </si>
 </sst>
 </file>
